--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform &amp; Data Engineer III</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b8d6e4d98fa228</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
@@ -678,87 +678,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect_Tempe,AZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Orrstown Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Towson, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Orrstown Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Towson, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
+          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dragonfly Health</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Dragonfly Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef3c2039b0fb0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
         </is>
       </c>
     </row>
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Software Engineer, Bet Engine</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Analyst - Data Intelligence</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Senior Software Engineer 2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>Stellar Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer 2</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stellar Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e39d63930b7f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1220b2bdf2efa606</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119e44dd3248d0</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Eventus WholeHealth</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb0ce03e10bd5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Sr Data Commercial Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393f62b59716a5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Eventus WholeHealth</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Commercial Engineer</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AHU Technologies</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technology Business Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jefferson, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>P3+Uplift</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,182 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Lowell, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Horizon Media, Inc.</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Palomar Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Edina, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EIS Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
+          <t>https://www.indeed.com/viewjob?jk=8d45eb216c68737b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Network For Organ Sharing</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect_Tempe,AZ</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>United Network For Organ Sharing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Technical Architect_Tempe,AZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>State Teachers' Retirement System</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Orrstown Bank</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Towson, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Orrstown Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Towson, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
+          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
+          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dragonfly Health</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Dragonfly Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
+          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=5a985a197da27b33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=75e60cd51a5aabad</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4c66a7703e5791</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Databrick</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer 2</t>
+          <t>Senior Software Engineer, Bet Engine</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stellar Health</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d555ebdaf6f923</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Systems Programmer Analyst l - Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brown Brothers Harriman</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
+          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Stellar Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
+          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT System Reliability Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
+          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eventus WholeHealth</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Data Commercial Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
+          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>P3+Uplift</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
+          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Eventus WholeHealth</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
+          <t>Sr Data Commercial Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AHU Technologies</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Horizon Media, Inc.</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6baf999dcc46c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,402 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lowell, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BrightSpring Health Services</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, ML Ops</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PathAI</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior ETL Developer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>STAR Autism Support</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>27.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc0184eaf514f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d45eb216c68737b</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
+          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Network For Organ Sharing</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect_Tempe,AZ</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>United Network For Organ Sharing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Technical Architect_Tempe,AZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>State Teachers' Retirement System</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
+          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>State Teachers' Retirement System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Orrstown Bank</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Towson, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Orrstown Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Towson, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
+          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
+          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dragonfly Health</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Dragonfly Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a985a197da27b33</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb56a973b20acc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e60cd51a5aabad</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4c66a7703e5791</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7e9ecc9b2a5055</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
         </is>
       </c>
     </row>
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Software Engineer, Bet Engine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer 2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Stellar Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer 2</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellar Health</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Softek International Inc</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
+          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
+          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Eventus WholeHealth</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Commercial Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,29 +2936,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
+          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Eventus WholeHealth</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Commercial Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT System Reliability Engineer</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6baf999dcc46c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AHU Technologies</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>P3+Uplift</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Software</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Ops</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PathAI</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>STAR Autism Support</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf50c444c6292e3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d96490d4c97f8fd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STAR Autism Support</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
+          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,41 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>United Network For Organ Sharing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect_Tempe,AZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United Network For Organ Sharing</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
+          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Architect_Tempe,AZ</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>State Teachers' Retirement System</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State Teachers' Retirement System</t>
+          <t>Orrstown Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Towson, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
+          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orrstown Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Towson, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
+          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
+          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dragonfly Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
+          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=75e60cd51a5aabad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb56a973b20acc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7737dd6535d2fd63</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Senior Software Engineer, Bet Engine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7e9ecc9b2a5055</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure Databrick</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
+          <t>https://www.indeed.com/viewjob?jk=393f62b59716a5a4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>Eventus WholeHealth</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer 2</t>
+          <t>Sr Data Commercial Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stellar Health</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Softek International Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eventus WholeHealth</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Data Commercial Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT System Reliability Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96bd7a58d09125</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>STAR Autism Support</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AHU Technologies</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3085,531 +3085,6 @@
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Collaboredge</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P3+Uplift</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Lowell, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Ops</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PathAI</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Gen AI Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior ETL Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>STAR Autism Support</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf50c444c6292e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d96490d4c97f8fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dec605ec7e7534</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=867542810b759ecf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb56a973b20acc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e60cd51a5aabad</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=5a985a197da27b33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Databrick</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7e9ecc9b2a5055</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7737dd6535d2fd63</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=3a341c0c6a783354</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Softek International Inc</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393f62b59716a5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96bd7a58d09125</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Ops</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PathAI</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior ETL Developer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>STAR Autism Support</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96bd7a58d09125</t>
+          <t>https://www.indeed.com/viewjob?jk=2d96490d4c97f8fd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STAR Autism Support</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3050,41 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Vertex AI, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=28c474e6ef0d9a03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer - Remote Opportunity!</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
+          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Network For Organ Sharing</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
+          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect_Tempe,AZ</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,104 +801,104 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
+          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Technical Architect_Tempe,AZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>State Teachers' Retirement System</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, Photon, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
+          <t>https://www.indeed.com/viewjob?jk=496e7cab1d90adc0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orrstown Bank</t>
+          <t>State Teachers' Retirement System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Towson, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, RDS, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dec605ec7e7534</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867542810b759ecf</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06626676d0ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,172 +1266,172 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb56a973b20acc</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior Software Engineer, Bet Engine</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Cloud Engineer - Professional Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a985a197da27b33</t>
+          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data - SF</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7e9ecc9b2a5055</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure Databrick</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
+          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Commercial Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
+          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a341c0c6a783354</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>STAR Autism Support</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,741 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eda731a8fe83cd61</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Softek International Inc</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Palomar Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>La Jolla, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Vitol</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Eventus WholeHealth</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Sr Data Commercial Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MGM Resorts International</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>IT System Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Nelnet</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96bd7a58d09125</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Ansible Automation Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>AHU Technologies</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Lowell, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior ETL Developer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Ops</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>PathAI</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>STAR Autism Support</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d96490d4c97f8fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>

--- a/results/job_matches_2026-09-12.xlsx
+++ b/results/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8582e8cd3f2da98</t>
+          <t>https://www.indeed.com/viewjob?jk=867542810b759ecf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Data Engineer</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, Splunk</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c2a0350b61ea90</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eacc86d237480d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer - Commercial Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7e9ecc9b2a5055</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Azure Databrick</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Databrick</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8994a35621e54353</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Bet Engine</t>
+          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995a42ced6baff4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
+          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Professional Services</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5310bd0a981c918</t>
+          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud (Sunnyvale, CA; US Remote)</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e38b299be118412</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Softek International Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a1a883fbc79044</t>
+          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>IT System Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Streams/Tasks, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b144b63a550174</t>
+          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Softek International Inc</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
+          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421ab27750f96f14</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>STAR Autism Support</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ce4072ed9216d</t>
+          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5afde5dbdaaea472</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT System Reliability Engineer</t>
+          <t>Senior ETL Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Commercial Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ELT, Terraform, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbb6ce6e14e1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2395a3423532a7f5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ansible Automation Platform Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4e35c4894614ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f7be3668078d3c0d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2070,251 +2070,6 @@
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc559018acf3f8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Ops</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>PathAI</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a003016846b78</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior ETL Developer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0af3aefe5076ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>STAR Autism Support</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>
